--- a/data/trans_camb/P44D-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P44D-Edad-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-41,89</t>
+          <t>-36,59</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,81</t>
+          <t>-1,53</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-21,16</t>
+          <t>-16,16</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 2,66</t>
+          <t>-62,07; 3,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-73,79; -13,64</t>
+          <t>-66,84; -9,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 54,11</t>
+          <t>-11,14; 51,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 9,5</t>
+          <t>-20,52; 9,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,73; 15,81</t>
+          <t>-26,11; 13,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-44,23; -8,03</t>
+          <t>-34,89; -2,13</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-95,59%</t>
+          <t>-83,48%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-16,51%</t>
+          <t>-13,97%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-86,82%</t>
+          <t>-66,31%</t>
         </is>
       </c>
     </row>
@@ -707,12 +707,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-92,86; 20,42</t>
+          <t>-92,47; 44,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -76,24</t>
+          <t>-95,69; -46,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-81,96; —</t>
+          <t>-79,64; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,9; 138,61</t>
+          <t>-73,02; 118,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-97,9; -56,61</t>
+          <t>-85,05; -6,91</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>5,13</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-23,96</t>
+          <t>-23,99</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-8,71</t>
+          <t>-8,41</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 35,1</t>
+          <t>-2,41; 34,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 13,53</t>
+          <t>-16,16; 13,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-47,72; -4,98</t>
+          <t>-46,58; -8,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-43,84; -6,34</t>
+          <t>-44,39; -8,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 14,83</t>
+          <t>-15,81; 13,38</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 0,73</t>
+          <t>-21,91; 1,16</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-74,95%</t>
+          <t>-75,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-44,58%</t>
+          <t>-43,02%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-48,92; —</t>
+          <t>-40,74; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,14; —</t>
+          <t>-61,89; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 7,08</t>
+          <t>-100,0; -15,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-87,08; -39,91</t>
+          <t>-87,56; -48,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 145,46</t>
+          <t>-56,72; 117,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-72,25; 7,4</t>
+          <t>-68,55; 11,2</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>-0,18</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 4,89</t>
+          <t>-24,05; 6,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 9,64</t>
+          <t>-23,43; 9,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 25,67</t>
+          <t>-11,29; 25,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,58; 8,0</t>
+          <t>-20,77; 8,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,19; 9,44</t>
+          <t>-12,52; 9,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 7,31</t>
+          <t>-12,85; 6,44</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-6,19%</t>
+          <t>-8,7%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>-2,03%</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1024,27 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,32; —</t>
+          <t>-75,39; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-76,34; —</t>
+          <t>-76,71; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,91; 277,06</t>
+          <t>-82,18; 279,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,41; 291,34</t>
+          <t>-65,02; 235,05</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-2,21</t>
+          <t>-2,23</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-12,56</t>
+          <t>-12,78</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-6,9</t>
+          <t>-7,04</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 9,5</t>
+          <t>-16,17; 9,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 4,63</t>
+          <t>-19,4; 5,19</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-32,04; 7,53</t>
+          <t>-32,01; 9,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-35,35; 0,05</t>
+          <t>-35,38; 0,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,59; 5,4</t>
+          <t>-16,51; 5,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,41; 0,02</t>
+          <t>-19,85; 0,74</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-30,13%</t>
+          <t>-30,46%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-75,53%</t>
+          <t>-76,87%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-60,18%</t>
+          <t>-61,34%</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-92,63; —</t>
+          <t>-88,83; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1190,17 +1190,17 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-93,51; 32,88</t>
+          <t>-93,65; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-89,29; 159,11</t>
+          <t>-86,38; 226,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-85,41; 8,86</t>
+          <t>-84,74; 25,31</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-6,33</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-10,56</t>
+          <t>-10,65</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-8,49</t>
+          <t>-6,82</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 9,68</t>
+          <t>-9,35; 9,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 0,1</t>
+          <t>-12,63; 3,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 3,3</t>
+          <t>-17,08; 3,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-20,33; -3,74</t>
+          <t>-19,65; -3,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 4,57</t>
+          <t>-9,59; 4,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-15,34; -2,63</t>
+          <t>-13,36; -1,36</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-48,73%</t>
+          <t>-24,45%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-58,93%</t>
+          <t>-59,45%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-55,06%</t>
+          <t>-44,26%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-48,54; 125,34</t>
+          <t>-52,31; 128,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-82,34; 0,04</t>
+          <t>-59,15; 54,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-73,88; 30,35</t>
+          <t>-71,51; 36,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-74,87; -31,79</t>
+          <t>-74,08; -26,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 39,88</t>
+          <t>-48,34; 45,4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-76,61; -28,23</t>
+          <t>-61,48; -12,38</t>
         </is>
       </c>
     </row>
